--- a/ECON13310/HP_GDP.xlsx
+++ b/ECON13310/HP_GDP.xlsx
@@ -1,24 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Oscar Galvez Soriano\Documents\Teaching\ECON13310\Lectures\L14\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Oscar Galvez Soriano\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{27D2C264-DCEE-4912-9A19-A06185E42231}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D222A78-3CEF-4CE0-A845-2BD862FD3F51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{985C0263-3C90-4CB2-8693-960ABF7D4D88}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{985C0263-3C90-4CB2-8693-960ABF7D4D88}"/>
   </bookViews>
   <sheets>
     <sheet name="MA_trend_GDP" sheetId="1" r:id="rId1"/>
     <sheet name="HP" sheetId="3" r:id="rId2"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId3"/>
-  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -88,12 +85,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -170,10 +168,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>MA_trend_GDP!$A$45:$A$76</c:f>
+              <c:f>MA_trend_GDP!$A$45:$A$78</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>1990</c:v>
                 </c:pt>
@@ -269,16 +267,22 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2023</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>MA_trend_GDP!$B$45:$B$76</c:f>
+              <c:f>MA_trend_GDP!$B$45:$B$78</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>10055.128500000001</c:v>
                 </c:pt>
@@ -340,40 +344,46 @@
                   <c:v>16349.110500000001</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>16789.750500000002</c:v>
+                  <c:v>16789.8</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>17052.410499999998</c:v>
+                  <c:v>17052.400000000001</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>17442.759250000003</c:v>
+                  <c:v>17442.8</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>17812.166999999998</c:v>
+                  <c:v>17812.2</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>18261.714249999997</c:v>
+                  <c:v>18261.7</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>18799.622000000003</c:v>
+                  <c:v>18799.599999999999</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>19141.67225</c:v>
+                  <c:v>19141.7</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>19612.102500000001</c:v>
+                  <c:v>19612.099999999999</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>20193.895249999998</c:v>
+                  <c:v>20193.900000000001</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>20692.086749999999</c:v>
+                  <c:v>20715.7</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>20234.074000000001</c:v>
+                  <c:v>20284.5</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>21407.692500000001</c:v>
+                  <c:v>21532.400000000001</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>22075.9</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>22723.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -414,10 +424,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>MA_trend_GDP!$A$45:$A$76</c:f>
+              <c:f>MA_trend_GDP!$A$45:$A$78</c:f>
               <c:numCache>
                 <c:formatCode>0</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>1990</c:v>
                 </c:pt>
@@ -513,16 +523,22 @@
                 </c:pt>
                 <c:pt idx="31">
                   <c:v>2021</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2022</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2023</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>MA_trend_GDP!$C$45:$C$76</c:f>
+              <c:f>MA_trend_GDP!$C$45:$C$78</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
-                <c:ptCount val="32"/>
+                <c:ptCount val="34"/>
                 <c:pt idx="0">
                   <c:v>9977.168450000001</c:v>
                 </c:pt>
@@ -578,46 +594,52 @@
                   <c:v>16462.829149999998</c:v>
                 </c:pt>
                 <c:pt idx="18">
-                  <c:v>16623.187750000001</c:v>
+                  <c:v>16623.197649999998</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>16747.040350000003</c:v>
+                  <c:v>16747.048149999999</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>16883.1031</c:v>
+                  <c:v>16883.119050000001</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>17089.239550000002</c:v>
+                  <c:v>17089.2621</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>17471.760300000002</c:v>
+                  <c:v>17471.78</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>17873.734600000003</c:v>
+                  <c:v>17873.739999999998</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>18291.586950000004</c:v>
+                  <c:v>18291.599999999999</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>18725.455599999998</c:v>
+                  <c:v>18725.46</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>19201.80125</c:v>
+                  <c:v>19201.8</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>19687.875749999999</c:v>
+                  <c:v>19692.599999999999</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>19974.766149999999</c:v>
+                  <c:v>19989.580000000002</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>20427.9702</c:v>
+                  <c:v>20467.72</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>20869.957000000002</c:v>
+                  <c:v>20960.48</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>21306.239450000001</c:v>
+                  <c:v>21466.44</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>21994.98</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>22708.159999999996</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1136,40 +1158,40 @@
                   <c:v>16349.110500000001</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>16789.750500000002</c:v>
+                  <c:v>16789.8</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>17052.410499999998</c:v>
+                  <c:v>17052.400000000001</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>17442.759250000003</c:v>
+                  <c:v>17442.8</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>17812.166999999998</c:v>
+                  <c:v>17812.2</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>18261.714249999997</c:v>
+                  <c:v>18261.7</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>18799.622000000003</c:v>
+                  <c:v>18799.599999999999</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>19141.67225</c:v>
+                  <c:v>19141.7</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>19612.102500000001</c:v>
+                  <c:v>19612.099999999999</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>20193.895249999998</c:v>
+                  <c:v>20193.900000000001</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>20692.086749999999</c:v>
+                  <c:v>20715.7</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>20234.074000000001</c:v>
+                  <c:v>20284.5</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>21407.692500000001</c:v>
+                  <c:v>21532.400000000001</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1693,1018 +1715,10 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
-    <sheetNames>
-      <sheetName val="GDP"/>
-      <sheetName val="Deflator"/>
-      <sheetName val="unemployment"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="1">
-          <cell r="E1" t="str">
-            <v>Annual GDP</v>
-          </cell>
-          <cell r="F1" t="str">
-            <v>Trend</v>
-          </cell>
-          <cell r="H1" t="str">
-            <v>Percentage deviation</v>
-          </cell>
-          <cell r="J1" t="str">
-            <v>Change in inflation</v>
-          </cell>
-          <cell r="M1" t="str">
-            <v>unemp_gap</v>
-          </cell>
-        </row>
-        <row r="15">
-          <cell r="H15">
-            <v>-1.5634909062796361E-2</v>
-          </cell>
-          <cell r="J15">
-            <v>-1.2045827326123693E-2</v>
-          </cell>
-          <cell r="M15">
-            <v>-0.47666666666666568</v>
-          </cell>
-        </row>
-        <row r="16">
-          <cell r="H16">
-            <v>-1.8518961508336276</v>
-          </cell>
-          <cell r="J16">
-            <v>-0.29577358562731249</v>
-          </cell>
-          <cell r="M16">
-            <v>0.91333333333333311</v>
-          </cell>
-        </row>
-        <row r="17">
-          <cell r="H17">
-            <v>-0.16384522050001399</v>
-          </cell>
-          <cell r="J17">
-            <v>0.14842261562559855</v>
-          </cell>
-          <cell r="M17">
-            <v>-0.15333333333333332</v>
-          </cell>
-        </row>
-        <row r="18">
-          <cell r="H18">
-            <v>-0.89458392382265761</v>
-          </cell>
-          <cell r="J18">
-            <v>-6.5017263537869852E-2</v>
-          </cell>
-          <cell r="M18">
-            <v>0.12833333333333385</v>
-          </cell>
-        </row>
-        <row r="19">
-          <cell r="H19">
-            <v>-1.0244878810945746</v>
-          </cell>
-          <cell r="J19">
-            <v>0.37369110359721791</v>
-          </cell>
-          <cell r="M19">
-            <v>0.22499999999999964</v>
-          </cell>
-        </row>
-        <row r="20">
-          <cell r="H20">
-            <v>0.24176354299374336</v>
-          </cell>
-          <cell r="J20">
-            <v>0.30896059932237208</v>
-          </cell>
-          <cell r="M20">
-            <v>-7.9999999999999183E-2</v>
-          </cell>
-        </row>
-        <row r="21">
-          <cell r="H21">
-            <v>1.5360991074659012</v>
-          </cell>
-          <cell r="J21">
-            <v>0.97468244402256765</v>
-          </cell>
-          <cell r="M21">
-            <v>-0.38000000000000034</v>
-          </cell>
-        </row>
-        <row r="22">
-          <cell r="H22">
-            <v>-0.34758529091937956</v>
-          </cell>
-          <cell r="J22">
-            <v>9.3632044369185152E-2</v>
-          </cell>
-          <cell r="M22">
-            <v>3.3333333333329662E-3</v>
-          </cell>
-        </row>
-        <row r="23">
-          <cell r="H23">
-            <v>1.1076690835849781</v>
-          </cell>
-          <cell r="J23">
-            <v>1.3613060970332436</v>
-          </cell>
-          <cell r="M23">
-            <v>-0.37500000000000044</v>
-          </cell>
-        </row>
-        <row r="24">
-          <cell r="H24">
-            <v>1.4055429348420088</v>
-          </cell>
-          <cell r="J24">
-            <v>0.64099445609346883</v>
-          </cell>
-          <cell r="M24">
-            <v>-0.87333333333333352</v>
-          </cell>
-        </row>
-        <row r="25">
-          <cell r="H25">
-            <v>-1.6953802679001466</v>
-          </cell>
-          <cell r="J25">
-            <v>0.38111324421759019</v>
-          </cell>
-          <cell r="M25">
-            <v>0.26666666666666661</v>
-          </cell>
-        </row>
-        <row r="26">
-          <cell r="H26">
-            <v>-1.9414499916966852</v>
-          </cell>
-          <cell r="J26">
-            <v>-0.21552921677796544</v>
-          </cell>
-          <cell r="M26">
-            <v>0.97333333333333361</v>
-          </cell>
-        </row>
-        <row r="27">
-          <cell r="H27">
-            <v>0.46101487737867636</v>
-          </cell>
-          <cell r="J27">
-            <v>-0.73937674045330137</v>
-          </cell>
-          <cell r="M27">
-            <v>0.19333333333333425</v>
-          </cell>
-        </row>
-        <row r="28">
-          <cell r="H28">
-            <v>3.4553629604614065</v>
-          </cell>
-          <cell r="J28">
-            <v>1.1489894073037465</v>
-          </cell>
-          <cell r="M28">
-            <v>-1.246666666666667</v>
-          </cell>
-        </row>
-        <row r="29">
-          <cell r="H29">
-            <v>-0.13575168840946827</v>
-          </cell>
-          <cell r="J29">
-            <v>3.5242140841135638</v>
-          </cell>
-          <cell r="M29">
-            <v>-0.81333333333333169</v>
-          </cell>
-        </row>
-        <row r="30">
-          <cell r="H30">
-            <v>-3.2144552641409598</v>
-          </cell>
-          <cell r="J30">
-            <v>0.26290216533615407</v>
-          </cell>
-          <cell r="M30">
-            <v>1.7299999999999995</v>
-          </cell>
-        </row>
-        <row r="31">
-          <cell r="H31">
-            <v>-0.99205091181183791</v>
-          </cell>
-          <cell r="J31">
-            <v>-3.7602475501028243</v>
-          </cell>
-          <cell r="M31">
-            <v>0.71333333333333204</v>
-          </cell>
-        </row>
-        <row r="32">
-          <cell r="H32">
-            <v>-0.13689326708781149</v>
-          </cell>
-          <cell r="J32">
-            <v>0.70847243105618407</v>
-          </cell>
-          <cell r="M32">
-            <v>2.1666666666667389E-2</v>
-          </cell>
-        </row>
-        <row r="33">
-          <cell r="H33">
-            <v>1.7523186570463871</v>
-          </cell>
-          <cell r="J33">
-            <v>0.82118673837254796</v>
-          </cell>
-          <cell r="M33">
-            <v>-0.7016666666666671</v>
-          </cell>
-        </row>
-        <row r="34">
-          <cell r="H34">
-            <v>1.8753117183937593</v>
-          </cell>
-          <cell r="J34">
-            <v>1.2653371161808202</v>
-          </cell>
-          <cell r="M34">
-            <v>-0.90166666666666728</v>
-          </cell>
-        </row>
-        <row r="35">
-          <cell r="H35">
-            <v>-0.13277482049866765</v>
-          </cell>
-          <cell r="J35">
-            <v>0.73214599945467995</v>
-          </cell>
-          <cell r="M35">
-            <v>-0.10833333333333339</v>
-          </cell>
-        </row>
-        <row r="36">
-          <cell r="H36">
-            <v>0.76655247314542141</v>
-          </cell>
-          <cell r="J36">
-            <v>0.43307913927961295</v>
-          </cell>
-          <cell r="M36">
-            <v>-0.37333333333333307</v>
-          </cell>
-        </row>
-        <row r="37">
-          <cell r="H37">
-            <v>-3.4539621398436458</v>
-          </cell>
-          <cell r="J37">
-            <v>-3.2870545027450229</v>
-          </cell>
-          <cell r="M37">
-            <v>1.3866666666666649</v>
-          </cell>
-        </row>
-        <row r="38">
-          <cell r="H38">
-            <v>-2.3311799354879157</v>
-          </cell>
-          <cell r="J38">
-            <v>-2.2584091847475785</v>
-          </cell>
-          <cell r="M38">
-            <v>1.2750000000000004</v>
-          </cell>
-        </row>
-        <row r="39">
-          <cell r="H39">
-            <v>1.1402994406464013</v>
-          </cell>
-          <cell r="J39">
-            <v>-0.31177679724221363</v>
-          </cell>
-          <cell r="M39">
-            <v>-0.69333333333333069</v>
-          </cell>
-        </row>
-        <row r="40">
-          <cell r="H40">
-            <v>0.80316185739444468</v>
-          </cell>
-          <cell r="J40">
-            <v>-0.44218810514500273</v>
-          </cell>
-          <cell r="M40">
-            <v>-0.30333333333333368</v>
-          </cell>
-        </row>
-        <row r="41">
-          <cell r="H41">
-            <v>-0.13347517272860615</v>
-          </cell>
-          <cell r="J41">
-            <v>-1.1516405765277238</v>
-          </cell>
-          <cell r="M41">
-            <v>0.32666666666666622</v>
-          </cell>
-        </row>
-        <row r="42">
-          <cell r="H42">
-            <v>-0.45116556688077314</v>
-          </cell>
-          <cell r="J42">
-            <v>0.46560121475855976</v>
-          </cell>
-          <cell r="M42">
-            <v>-4.8333333333332895E-2</v>
-          </cell>
-        </row>
-        <row r="43">
-          <cell r="H43">
-            <v>0.3864250651567544</v>
-          </cell>
-          <cell r="J43">
-            <v>1.0485813130091559</v>
-          </cell>
-          <cell r="M43">
-            <v>-0.41666666666666696</v>
-          </cell>
-        </row>
-        <row r="44">
-          <cell r="H44">
-            <v>1.4796246764618215</v>
-          </cell>
-          <cell r="J44">
-            <v>0.39431591049294834</v>
-          </cell>
-          <cell r="M44">
-            <v>-0.62000000000000011</v>
-          </cell>
-        </row>
-        <row r="45">
-          <cell r="D45">
-            <v>1990</v>
-          </cell>
-          <cell r="E45">
-            <v>10055.128500000001</v>
-          </cell>
-          <cell r="F45">
-            <v>9977.168450000001</v>
-          </cell>
-          <cell r="H45">
-            <v>0.78138452197827402</v>
-          </cell>
-          <cell r="J45">
-            <v>-0.17769844388177969</v>
-          </cell>
-          <cell r="M45">
-            <v>-0.52500000000000036</v>
-          </cell>
-        </row>
-        <row r="46">
-          <cell r="D46">
-            <v>1991</v>
-          </cell>
-          <cell r="E46">
-            <v>10044.237499999999</v>
-          </cell>
-          <cell r="F46">
-            <v>10210.118850000001</v>
-          </cell>
-          <cell r="H46">
-            <v>-1.6246759948342959</v>
-          </cell>
-          <cell r="J46">
-            <v>-0.36272145117075549</v>
-          </cell>
-          <cell r="M46">
-            <v>0.42499999999999893</v>
-          </cell>
-        </row>
-        <row r="47">
-          <cell r="D47">
-            <v>1992</v>
-          </cell>
-          <cell r="E47">
-            <v>10398.046250000001</v>
-          </cell>
-          <cell r="F47">
-            <v>10459.247449999999</v>
-          </cell>
-          <cell r="H47">
-            <v>-0.5851396125062297</v>
-          </cell>
-          <cell r="J47">
-            <v>-1.1022436794407175</v>
-          </cell>
-          <cell r="M47">
-            <v>0.8983333333333352</v>
-          </cell>
-        </row>
-        <row r="48">
-          <cell r="D48">
-            <v>1993</v>
-          </cell>
-          <cell r="E48">
-            <v>10684.178749999999</v>
-          </cell>
-          <cell r="F48">
-            <v>10730.824199999999</v>
-          </cell>
-          <cell r="H48">
-            <v>-0.43468655464507555</v>
-          </cell>
-          <cell r="J48">
-            <v>9.2761857705259132E-2</v>
-          </cell>
-          <cell r="M48">
-            <v>0.3199999999999994</v>
-          </cell>
-        </row>
-        <row r="49">
-          <cell r="D49">
-            <v>1994</v>
-          </cell>
-          <cell r="E49">
-            <v>11114.64625</v>
-          </cell>
-          <cell r="F49">
-            <v>11090.6965</v>
-          </cell>
-          <cell r="H49">
-            <v>0.21594450808386803</v>
-          </cell>
-          <cell r="J49">
-            <v>-0.23719026160147205</v>
-          </cell>
-          <cell r="M49">
-            <v>-0.20000000000000018</v>
-          </cell>
-        </row>
-        <row r="50">
-          <cell r="D50">
-            <v>1995</v>
-          </cell>
-          <cell r="E50">
-            <v>11413.01225</v>
-          </cell>
-          <cell r="F50">
-            <v>11485.147150000001</v>
-          </cell>
-          <cell r="H50">
-            <v>-0.62807118670657103</v>
-          </cell>
-          <cell r="J50">
-            <v>-3.6968359174993637E-2</v>
-          </cell>
-          <cell r="M50">
-            <v>-0.19833333333333325</v>
-          </cell>
-        </row>
-        <row r="51">
-          <cell r="D51">
-            <v>1996</v>
-          </cell>
-          <cell r="E51">
-            <v>11843.599</v>
-          </cell>
-          <cell r="F51">
-            <v>11933.286550000001</v>
-          </cell>
-          <cell r="H51">
-            <v>-0.75157459451101971</v>
-          </cell>
-          <cell r="J51">
-            <v>-0.26716313040655582</v>
-          </cell>
-          <cell r="M51">
-            <v>0.10000000000000053</v>
-          </cell>
-        </row>
-        <row r="52">
-          <cell r="D52">
-            <v>1997</v>
-          </cell>
-          <cell r="E52">
-            <v>12370.299500000001</v>
-          </cell>
-          <cell r="F52">
-            <v>12419.112100000002</v>
-          </cell>
-          <cell r="H52">
-            <v>-0.39304420160601578</v>
-          </cell>
-          <cell r="J52">
-            <v>-0.10477348496855665</v>
-          </cell>
-          <cell r="M52">
-            <v>9.9999999999988987E-3</v>
-          </cell>
-        </row>
-        <row r="53">
-          <cell r="D53">
-            <v>1998</v>
-          </cell>
-          <cell r="E53">
-            <v>12924.875749999999</v>
-          </cell>
-          <cell r="F53">
-            <v>12955.716250000001</v>
-          </cell>
-          <cell r="H53">
-            <v>-0.23804550365945273</v>
-          </cell>
-          <cell r="J53">
-            <v>-0.60180119725843362</v>
-          </cell>
-          <cell r="M53">
-            <v>-0.10666666666666735</v>
-          </cell>
-        </row>
-        <row r="54">
-          <cell r="D54">
-            <v>1999</v>
-          </cell>
-          <cell r="E54">
-            <v>13543.774000000001</v>
-          </cell>
-          <cell r="F54">
-            <v>13433.14165</v>
-          </cell>
-          <cell r="H54">
-            <v>0.8235776327126102</v>
-          </cell>
-          <cell r="J54">
-            <v>0.29128813457686142</v>
-          </cell>
-          <cell r="M54">
-            <v>-0.25666666666666593</v>
-          </cell>
-        </row>
-        <row r="55">
-          <cell r="D55">
-            <v>2000</v>
-          </cell>
-          <cell r="E55">
-            <v>14096.032999999999</v>
-          </cell>
-          <cell r="F55">
-            <v>13853.624050000002</v>
-          </cell>
-          <cell r="H55">
-            <v>1.7497872695628494</v>
-          </cell>
-          <cell r="J55">
-            <v>0.85073448692245535</v>
-          </cell>
-          <cell r="M55">
-            <v>-0.67500000000000115</v>
-          </cell>
-        </row>
-        <row r="56">
-          <cell r="D56">
-            <v>2001</v>
-          </cell>
-          <cell r="E56">
-            <v>14230.726000000001</v>
-          </cell>
-          <cell r="F56">
-            <v>14244.1114</v>
-          </cell>
-          <cell r="H56">
-            <v>-9.3971463885063472E-2</v>
-          </cell>
-          <cell r="J56">
-            <v>-1.3058989836167711E-2</v>
-          </cell>
-          <cell r="M56">
-            <v>-0.19833333333333414</v>
-          </cell>
-        </row>
-        <row r="57">
-          <cell r="D57">
-            <v>2002</v>
-          </cell>
-          <cell r="E57">
-            <v>14472.711500000001</v>
-          </cell>
-          <cell r="F57">
-            <v>14625.308049999998</v>
-          </cell>
-          <cell r="H57">
-            <v>-1.0433732368460888</v>
-          </cell>
-          <cell r="J57">
-            <v>-0.69915886209444</v>
-          </cell>
-          <cell r="M57">
-            <v>0.57833333333333403</v>
-          </cell>
-        </row>
-        <row r="58">
-          <cell r="D58">
-            <v>2003</v>
-          </cell>
-          <cell r="E58">
-            <v>14877.3125</v>
-          </cell>
-          <cell r="F58">
-            <v>15003.692950000001</v>
-          </cell>
-          <cell r="H58">
-            <v>-0.84232895475244018</v>
-          </cell>
-          <cell r="J58">
-            <v>0.42118772593868758</v>
-          </cell>
-          <cell r="M58">
-            <v>0.56333333333333435</v>
-          </cell>
-        </row>
-        <row r="59">
-          <cell r="D59">
-            <v>2004</v>
-          </cell>
-          <cell r="E59">
-            <v>15449.757249999999</v>
-          </cell>
-          <cell r="F59">
-            <v>15444.177250000002</v>
-          </cell>
-          <cell r="H59">
-            <v>3.6130121466951493E-2</v>
-          </cell>
-          <cell r="J59">
-            <v>0.71495866210116166</v>
-          </cell>
-          <cell r="M59">
-            <v>0.13999999999999968</v>
-          </cell>
-        </row>
-        <row r="60">
-          <cell r="D60">
-            <v>2005</v>
-          </cell>
-          <cell r="E60">
-            <v>15987.9575</v>
-          </cell>
-          <cell r="F60">
-            <v>15902.124050000002</v>
-          </cell>
-          <cell r="H60">
-            <v>0.53976091325987519</v>
-          </cell>
-          <cell r="J60">
-            <v>0.44551830354642163</v>
-          </cell>
-          <cell r="M60">
-            <v>-8.5000000000000853E-2</v>
-          </cell>
-        </row>
-        <row r="61">
-          <cell r="D61">
-            <v>2006</v>
-          </cell>
-          <cell r="E61">
-            <v>16433.147499999999</v>
-          </cell>
-          <cell r="F61">
-            <v>16282.958499999999</v>
-          </cell>
-          <cell r="H61">
-            <v>0.92236923652418767</v>
-          </cell>
-          <cell r="J61">
-            <v>-5.1148468805739533E-2</v>
-          </cell>
-          <cell r="M61">
-            <v>-0.52166666666666739</v>
-          </cell>
-        </row>
-        <row r="62">
-          <cell r="D62">
-            <v>2007</v>
-          </cell>
-          <cell r="E62">
-            <v>16762.445500000002</v>
-          </cell>
-          <cell r="F62">
-            <v>16462.829149999998</v>
-          </cell>
-          <cell r="H62">
-            <v>1.8199566263493898</v>
-          </cell>
-          <cell r="J62">
-            <v>-0.3741561681380734</v>
-          </cell>
-          <cell r="M62">
-            <v>-1.2616666666666658</v>
-          </cell>
-        </row>
-        <row r="63">
-          <cell r="D63">
-            <v>2008</v>
-          </cell>
-          <cell r="E63">
-            <v>16781.48475</v>
-          </cell>
-          <cell r="F63">
-            <v>16623.187750000001</v>
-          </cell>
-          <cell r="H63">
-            <v>0.95226621019183677</v>
-          </cell>
-          <cell r="J63">
-            <v>-0.78255106386806439</v>
-          </cell>
-          <cell r="M63">
-            <v>-0.98333333333333428</v>
-          </cell>
-        </row>
-        <row r="64">
-          <cell r="D64">
-            <v>2009</v>
-          </cell>
-          <cell r="E64">
-            <v>16349.110500000001</v>
-          </cell>
-          <cell r="F64">
-            <v>16747.040350000003</v>
-          </cell>
-          <cell r="H64">
-            <v>-2.3761204468585531</v>
-          </cell>
-          <cell r="J64">
-            <v>-1.3101091150769184</v>
-          </cell>
-          <cell r="M64">
-            <v>1.634999999999998</v>
-          </cell>
-        </row>
-        <row r="65">
-          <cell r="D65">
-            <v>2010</v>
-          </cell>
-          <cell r="E65">
-            <v>16789.750500000002</v>
-          </cell>
-          <cell r="F65">
-            <v>16883.1031</v>
-          </cell>
-          <cell r="H65">
-            <v>-0.55293508217691534</v>
-          </cell>
-          <cell r="J65">
-            <v>0.59809605004443878</v>
-          </cell>
-          <cell r="M65">
-            <v>1.2683333333333326</v>
-          </cell>
-        </row>
-        <row r="66">
-          <cell r="D66">
-            <v>2011</v>
-          </cell>
-          <cell r="E66">
-            <v>17052.410499999998</v>
-          </cell>
-          <cell r="F66">
-            <v>17089.239550000002</v>
-          </cell>
-          <cell r="H66">
-            <v>-0.21551017464673503</v>
-          </cell>
-          <cell r="J66">
-            <v>0.8478289651993931</v>
-          </cell>
-          <cell r="M66">
-            <v>0.28166666666666629</v>
-          </cell>
-        </row>
-        <row r="67">
-          <cell r="D67">
-            <v>2012</v>
-          </cell>
-          <cell r="E67">
-            <v>17442.759250000003</v>
-          </cell>
-          <cell r="F67">
-            <v>17471.760300000002</v>
-          </cell>
-          <cell r="H67">
-            <v>-0.16598814030203321</v>
-          </cell>
-          <cell r="J67">
-            <v>-0.20019746044501741</v>
-          </cell>
-          <cell r="M67">
-            <v>4.8333333333333783E-2</v>
-          </cell>
-        </row>
-        <row r="68">
-          <cell r="D68">
-            <v>2013</v>
-          </cell>
-          <cell r="E68">
-            <v>17812.166999999998</v>
-          </cell>
-          <cell r="F68">
-            <v>17873.734600000003</v>
-          </cell>
-          <cell r="H68">
-            <v>-0.34445851064615091</v>
-          </cell>
-          <cell r="J68">
-            <v>-0.16069120463269027</v>
-          </cell>
-          <cell r="M68">
-            <v>0.19833333333333325</v>
-          </cell>
-        </row>
-        <row r="69">
-          <cell r="D69">
-            <v>2014</v>
-          </cell>
-          <cell r="E69">
-            <v>18261.714249999997</v>
-          </cell>
-          <cell r="F69">
-            <v>18291.586950000004</v>
-          </cell>
-          <cell r="H69">
-            <v>-0.16331387802307204</v>
-          </cell>
-          <cell r="J69">
-            <v>3.9048261676266627E-2</v>
-          </cell>
-          <cell r="M69">
-            <v>-0.1899999999999995</v>
-          </cell>
-        </row>
-        <row r="70">
-          <cell r="D70">
-            <v>2015</v>
-          </cell>
-          <cell r="E70">
-            <v>18799.622000000003</v>
-          </cell>
-          <cell r="F70">
-            <v>18725.455599999998</v>
-          </cell>
-          <cell r="H70">
-            <v>0.39607260610527162</v>
-          </cell>
-          <cell r="J70">
-            <v>-0.81281789472136268</v>
-          </cell>
-          <cell r="M70">
-            <v>-0.33000000000000096</v>
-          </cell>
-        </row>
-        <row r="71">
-          <cell r="D71">
-            <v>2016</v>
-          </cell>
-          <cell r="E71">
-            <v>19141.67225</v>
-          </cell>
-          <cell r="F71">
-            <v>19201.80125</v>
-          </cell>
-          <cell r="H71">
-            <v>-0.31314249750398193</v>
-          </cell>
-          <cell r="J71">
-            <v>2.2290704278171702E-2</v>
-          </cell>
-          <cell r="M71">
-            <v>-3.6666666666667069E-2</v>
-          </cell>
-        </row>
-        <row r="72">
-          <cell r="D72">
-            <v>2017</v>
-          </cell>
-          <cell r="E72">
-            <v>19612.102500000001</v>
-          </cell>
-          <cell r="F72">
-            <v>19687.875749999999</v>
-          </cell>
-          <cell r="H72">
-            <v>-0.38487265443047292</v>
-          </cell>
-          <cell r="J72">
-            <v>0.83998306862873573</v>
-          </cell>
-          <cell r="M72">
-            <v>-5.6666666666666643E-2</v>
-          </cell>
-        </row>
-        <row r="73">
-          <cell r="D73">
-            <v>2018</v>
-          </cell>
-          <cell r="E73">
-            <v>20193.895249999998</v>
-          </cell>
-          <cell r="F73">
-            <v>19974.766149999999</v>
-          </cell>
-          <cell r="H73">
-            <v>1.097029614036299</v>
-          </cell>
-          <cell r="J73">
-            <v>0.50050519640476576</v>
-          </cell>
-          <cell r="M73">
-            <v>-1.0866666666666673</v>
-          </cell>
-        </row>
-        <row r="74">
-          <cell r="D74">
-            <v>2019</v>
-          </cell>
-          <cell r="E74">
-            <v>20692.086749999999</v>
-          </cell>
-          <cell r="F74">
-            <v>20427.9702</v>
-          </cell>
-          <cell r="H74">
-            <v>1.2929162683035382</v>
-          </cell>
-          <cell r="J74">
-            <v>-0.61245545551416036</v>
-          </cell>
-          <cell r="M74">
-            <v>-1.3983333333333325</v>
-          </cell>
-        </row>
-        <row r="75">
-          <cell r="D75">
-            <v>2020</v>
-          </cell>
-          <cell r="E75">
-            <v>20234.074000000001</v>
-          </cell>
-          <cell r="F75">
-            <v>20869.957000000002</v>
-          </cell>
-          <cell r="H75">
-            <v>-3.0468821761348219</v>
-          </cell>
-          <cell r="J75">
-            <v>-0.35845378223677837</v>
-          </cell>
-          <cell r="M75">
-            <v>3.163333333333334</v>
-          </cell>
-        </row>
-        <row r="76">
-          <cell r="D76">
-            <v>2021</v>
-          </cell>
-          <cell r="E76">
-            <v>21407.692500000001</v>
-          </cell>
-          <cell r="F76">
-            <v>21306.239450000001</v>
-          </cell>
-          <cell r="H76">
-            <v>0.47616591486302884</v>
-          </cell>
-          <cell r="J76">
-            <v>3.2651760315752565</v>
-          </cell>
-          <cell r="M76">
-            <v>0.47500000000000142</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2742,7 +1756,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -2848,7 +1862,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2990,7 +2004,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4571,7 +3585,7 @@
       </c>
       <c r="C63" s="4">
         <f t="shared" si="0"/>
-        <v>16623.187750000001</v>
+        <v>16623.197649999998</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.2">
@@ -4583,7 +3597,7 @@
       </c>
       <c r="C64" s="4">
         <f t="shared" si="0"/>
-        <v>16747.040350000003</v>
+        <v>16747.048149999999</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.2">
@@ -4591,11 +3605,11 @@
         <v>2010</v>
       </c>
       <c r="B65" s="4">
-        <v>16789.750500000002</v>
+        <v>16789.8</v>
       </c>
       <c r="C65" s="4">
         <f t="shared" si="0"/>
-        <v>16883.1031</v>
+        <v>16883.119050000001</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.2">
@@ -4603,11 +3617,11 @@
         <v>2011</v>
       </c>
       <c r="B66" s="4">
-        <v>17052.410499999998</v>
+        <v>17052.400000000001</v>
       </c>
       <c r="C66" s="4">
         <f t="shared" si="0"/>
-        <v>17089.239550000002</v>
+        <v>17089.2621</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.2">
@@ -4615,11 +3629,11 @@
         <v>2012</v>
       </c>
       <c r="B67" s="4">
-        <v>17442.759250000003</v>
+        <v>17442.8</v>
       </c>
       <c r="C67" s="4">
         <f t="shared" si="0"/>
-        <v>17471.760300000002</v>
+        <v>17471.78</v>
       </c>
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.2">
@@ -4627,11 +3641,11 @@
         <v>2013</v>
       </c>
       <c r="B68" s="4">
-        <v>17812.166999999998</v>
+        <v>17812.2</v>
       </c>
       <c r="C68" s="4">
         <f t="shared" si="0"/>
-        <v>17873.734600000003</v>
+        <v>17873.739999999998</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.2">
@@ -4639,11 +3653,11 @@
         <v>2014</v>
       </c>
       <c r="B69" s="4">
-        <v>18261.714249999997</v>
+        <v>18261.7</v>
       </c>
       <c r="C69" s="4">
-        <f t="shared" ref="C69:C76" si="1">AVERAGE(B67:B71)</f>
-        <v>18291.586950000004</v>
+        <f t="shared" ref="C69:C78" si="1">AVERAGE(B67:B71)</f>
+        <v>18291.599999999999</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.2">
@@ -4651,11 +3665,11 @@
         <v>2015</v>
       </c>
       <c r="B70" s="4">
-        <v>18799.622000000003</v>
+        <v>18799.599999999999</v>
       </c>
       <c r="C70" s="4">
         <f t="shared" si="1"/>
-        <v>18725.455599999998</v>
+        <v>18725.46</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.2">
@@ -4663,11 +3677,11 @@
         <v>2016</v>
       </c>
       <c r="B71" s="4">
-        <v>19141.67225</v>
+        <v>19141.7</v>
       </c>
       <c r="C71" s="4">
         <f t="shared" si="1"/>
-        <v>19201.80125</v>
+        <v>19201.8</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.2">
@@ -4675,11 +3689,11 @@
         <v>2017</v>
       </c>
       <c r="B72" s="4">
-        <v>19612.102500000001</v>
+        <v>19612.099999999999</v>
       </c>
       <c r="C72" s="4">
         <f t="shared" si="1"/>
-        <v>19687.875749999999</v>
+        <v>19692.599999999999</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.2">
@@ -4687,11 +3701,11 @@
         <v>2018</v>
       </c>
       <c r="B73" s="4">
-        <v>20193.895249999998</v>
+        <v>20193.900000000001</v>
       </c>
       <c r="C73" s="4">
         <f t="shared" si="1"/>
-        <v>19974.766149999999</v>
+        <v>19989.580000000002</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.2">
@@ -4699,11 +3713,11 @@
         <v>2019</v>
       </c>
       <c r="B74" s="4">
-        <v>20692.086749999999</v>
+        <v>20715.7</v>
       </c>
       <c r="C74" s="4">
         <f t="shared" si="1"/>
-        <v>20427.9702</v>
+        <v>20467.72</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.2">
@@ -4711,11 +3725,11 @@
         <v>2020</v>
       </c>
       <c r="B75" s="4">
-        <v>20234.074000000001</v>
+        <v>20284.5</v>
       </c>
       <c r="C75" s="4">
         <f t="shared" si="1"/>
-        <v>20869.957000000002</v>
+        <v>20960.48</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.2">
@@ -4723,11 +3737,11 @@
         <v>2021</v>
       </c>
       <c r="B76" s="4">
-        <v>21407.692500000001</v>
+        <v>21532.400000000001</v>
       </c>
       <c r="C76" s="4">
         <f t="shared" si="1"/>
-        <v>21306.239450000001</v>
+        <v>21466.44</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.2">
@@ -4735,25 +3749,41 @@
         <v>2022</v>
       </c>
       <c r="B77" s="4">
-        <v>21822.036500000002</v>
-      </c>
-      <c r="C77" s="4"/>
+        <v>22075.9</v>
+      </c>
+      <c r="C77" s="4">
+        <f t="shared" si="1"/>
+        <v>21994.98</v>
+      </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A78" s="3">
         <v>2023</v>
       </c>
       <c r="B78" s="4">
-        <v>22375.307499999999</v>
-      </c>
-      <c r="C78" s="4"/>
+        <v>22723.7</v>
+      </c>
+      <c r="C78" s="4">
+        <f t="shared" si="1"/>
+        <v>22708.159999999996</v>
+      </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A79" s="2"/>
+      <c r="A79" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B79">
+        <v>23358.400000000001</v>
+      </c>
       <c r="C79" s="2"/>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A80" s="2"/>
+      <c r="A80" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B80">
+        <v>23850.400000000001</v>
+      </c>
       <c r="C80" s="2"/>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.2">
@@ -5681,7 +4711,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{722FD664-3E5D-407C-8BDE-0367812B6003}">
-  <dimension ref="A1:C309"/>
+  <dimension ref="A1:S309"/>
   <sheetFormatPr defaultColWidth="20.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
@@ -7091,7 +6121,7 @@
         <v>2010</v>
       </c>
       <c r="B65" s="4">
-        <v>16789.750500000002</v>
+        <v>16789.8</v>
       </c>
       <c r="C65" s="4"/>
     </row>
@@ -7100,7 +6130,7 @@
         <v>2011</v>
       </c>
       <c r="B66" s="4">
-        <v>17052.410499999998</v>
+        <v>17052.400000000001</v>
       </c>
       <c r="C66" s="4"/>
     </row>
@@ -7109,7 +6139,7 @@
         <v>2012</v>
       </c>
       <c r="B67" s="4">
-        <v>17442.759250000003</v>
+        <v>17442.8</v>
       </c>
       <c r="C67" s="4"/>
     </row>
@@ -7118,7 +6148,7 @@
         <v>2013</v>
       </c>
       <c r="B68" s="4">
-        <v>17812.166999999998</v>
+        <v>17812.2</v>
       </c>
       <c r="C68" s="4"/>
     </row>
@@ -7127,7 +6157,7 @@
         <v>2014</v>
       </c>
       <c r="B69" s="4">
-        <v>18261.714249999997</v>
+        <v>18261.7</v>
       </c>
       <c r="C69" s="4"/>
     </row>
@@ -7136,7 +6166,7 @@
         <v>2015</v>
       </c>
       <c r="B70" s="4">
-        <v>18799.622000000003</v>
+        <v>18799.599999999999</v>
       </c>
       <c r="C70" s="4"/>
     </row>
@@ -7145,7 +6175,7 @@
         <v>2016</v>
       </c>
       <c r="B71" s="4">
-        <v>19141.67225</v>
+        <v>19141.7</v>
       </c>
       <c r="C71" s="4"/>
     </row>
@@ -7154,7 +6184,7 @@
         <v>2017</v>
       </c>
       <c r="B72" s="4">
-        <v>19612.102500000001</v>
+        <v>19612.099999999999</v>
       </c>
       <c r="C72" s="4"/>
     </row>
@@ -7163,7 +6193,7 @@
         <v>2018</v>
       </c>
       <c r="B73" s="4">
-        <v>20193.895249999998</v>
+        <v>20193.900000000001</v>
       </c>
       <c r="C73" s="4"/>
     </row>
@@ -7172,7 +6202,7 @@
         <v>2019</v>
       </c>
       <c r="B74" s="4">
-        <v>20692.086749999999</v>
+        <v>20715.7</v>
       </c>
       <c r="C74" s="4"/>
     </row>
@@ -7181,7 +6211,7 @@
         <v>2020</v>
       </c>
       <c r="B75" s="4">
-        <v>20234.074000000001</v>
+        <v>20284.5</v>
       </c>
       <c r="C75" s="4"/>
     </row>
@@ -7190,7 +6220,7 @@
         <v>2021</v>
       </c>
       <c r="B76" s="4">
-        <v>21407.692500000001</v>
+        <v>21532.400000000001</v>
       </c>
       <c r="C76" s="4"/>
     </row>
@@ -7199,7 +6229,7 @@
         <v>2022</v>
       </c>
       <c r="B77" s="4">
-        <v>21822.036500000002</v>
+        <v>22075.9</v>
       </c>
       <c r="C77" s="4"/>
     </row>
@@ -7208,143 +6238,186 @@
         <v>2023</v>
       </c>
       <c r="B78" s="4">
-        <v>22375.307499999999</v>
+        <v>22723.7</v>
       </c>
       <c r="C78" s="4"/>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A79" s="2"/>
+      <c r="A79" s="3">
+        <v>2024</v>
+      </c>
+      <c r="B79" s="4">
+        <v>23358.400000000001</v>
+      </c>
       <c r="C79" s="2"/>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A80" s="2"/>
+      <c r="A80" s="3">
+        <v>2025</v>
+      </c>
+      <c r="B80" s="4">
+        <v>23850.400000000001</v>
+      </c>
       <c r="C80" s="2"/>
     </row>
-    <row r="81" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A81" s="2"/>
       <c r="C81" s="2"/>
     </row>
-    <row r="82" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A82" s="2"/>
       <c r="C82" s="2"/>
     </row>
-    <row r="83" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A83" s="2"/>
       <c r="C83" s="2"/>
     </row>
-    <row r="84" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A84" s="2"/>
       <c r="C84" s="2"/>
     </row>
-    <row r="85" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A85" s="2"/>
       <c r="C85" s="2"/>
     </row>
-    <row r="86" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A86" s="2"/>
       <c r="C86" s="2"/>
     </row>
-    <row r="87" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A87" s="2"/>
       <c r="C87" s="2"/>
     </row>
-    <row r="88" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A88" s="2"/>
       <c r="C88" s="2"/>
-    </row>
-    <row r="89" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E88" s="5"/>
+    </row>
+    <row r="89" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A89" s="2"/>
       <c r="C89" s="2"/>
-    </row>
-    <row r="90" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E89" s="5"/>
+      <c r="F89" s="5"/>
+      <c r="G89" s="5"/>
+      <c r="H89" s="5"/>
+      <c r="I89" s="5"/>
+      <c r="J89" s="5"/>
+      <c r="K89" s="5"/>
+      <c r="L89" s="5"/>
+      <c r="M89" s="5"/>
+      <c r="N89" s="5"/>
+      <c r="O89" s="5"/>
+      <c r="P89" s="5"/>
+      <c r="Q89" s="5"/>
+    </row>
+    <row r="90" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A90" s="2"/>
       <c r="C90" s="2"/>
     </row>
-    <row r="91" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A91" s="2"/>
       <c r="C91" s="2"/>
     </row>
-    <row r="92" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A92" s="2"/>
       <c r="C92" s="2"/>
     </row>
-    <row r="93" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A93" s="2"/>
       <c r="C93" s="2"/>
-    </row>
-    <row r="94" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E93" s="5"/>
+    </row>
+    <row r="94" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A94" s="2"/>
       <c r="C94" s="2"/>
     </row>
-    <row r="95" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A95" s="2"/>
       <c r="C95" s="2"/>
     </row>
-    <row r="96" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A96" s="2"/>
       <c r="C96" s="2"/>
     </row>
-    <row r="97" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A97" s="2"/>
       <c r="C97" s="2"/>
-    </row>
-    <row r="98" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E97" s="5"/>
+    </row>
+    <row r="98" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A98" s="2"/>
       <c r="C98" s="2"/>
     </row>
-    <row r="99" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A99" s="2"/>
       <c r="C99" s="2"/>
     </row>
-    <row r="100" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A100" s="2"/>
       <c r="C100" s="2"/>
     </row>
-    <row r="101" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A101" s="2"/>
       <c r="C101" s="2"/>
-    </row>
-    <row r="102" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="E101" s="5"/>
+    </row>
+    <row r="102" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A102" s="2"/>
       <c r="C102" s="2"/>
     </row>
-    <row r="103" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A103" s="2"/>
       <c r="C103" s="2"/>
     </row>
-    <row r="104" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A104" s="2"/>
       <c r="C104" s="2"/>
-    </row>
-    <row r="105" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="D104" s="5"/>
+      <c r="E104" s="5"/>
+      <c r="F104" s="5"/>
+      <c r="G104" s="5"/>
+      <c r="H104" s="5"/>
+      <c r="I104" s="5"/>
+      <c r="J104" s="5"/>
+      <c r="K104" s="5"/>
+      <c r="L104" s="5"/>
+      <c r="M104" s="5"/>
+      <c r="N104" s="5"/>
+      <c r="O104" s="5"/>
+      <c r="P104" s="5"/>
+      <c r="Q104" s="5"/>
+      <c r="R104" s="5"/>
+      <c r="S104" s="5"/>
+    </row>
+    <row r="105" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A105" s="2"/>
       <c r="C105" s="2"/>
     </row>
-    <row r="106" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A106" s="2"/>
       <c r="C106" s="2"/>
     </row>
-    <row r="107" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A107" s="2"/>
       <c r="C107" s="2"/>
     </row>
-    <row r="108" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A108" s="2"/>
       <c r="C108" s="2"/>
     </row>
-    <row r="109" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A109" s="2"/>
       <c r="C109" s="2"/>
     </row>
-    <row r="110" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A110" s="2"/>
       <c r="C110" s="2"/>
     </row>
-    <row r="111" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A111" s="2"/>
       <c r="C111" s="2"/>
     </row>
-    <row r="112" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A112" s="2"/>
       <c r="C112" s="2"/>
     </row>
